--- a/4 четверть_9_JavaScript_Vue 3.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B77FC4-025C-4E3C-AAAE-B023B33C954A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A1598B-45A4-45D4-A55C-982CA60106EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="192" yWindow="-216" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="База" sheetId="12" r:id="rId1"/>
     <sheet name="Vue Css" sheetId="13" r:id="rId2"/>
     <sheet name="Теория" sheetId="14" r:id="rId3"/>
-    <sheet name="template" sheetId="15" r:id="rId4"/>
+    <sheet name="Vue blank template" sheetId="15" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="288">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -5804,17 +5804,72 @@
     }
 });</t>
   </si>
+  <si>
+    <t xml:space="preserve">        changeText(scope, e, type=false) {
+            let dataName = (!type) ? 'usersDataFilteredComp' : 'ipAndPassArray';
+            let res = this[dataName].map(i =&gt; ({...i}));
+            let index = scope.$index;
+            let prop = scope.column.property;
+            res[index][prop] = e.target ? e.target.value : e;
+            this[dataName] = res;
+        },</t>
+  </si>
+  <si>
+    <t>Reflection</t>
+  </si>
+  <si>
+    <t>Удобно!</t>
+  </si>
+  <si>
+    <t>Поверхностное копирование - удобно!</t>
+  </si>
+  <si>
+    <r>
+      <t>let res = this[dataName].map(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i =&gt; ({...i})</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6117,10 +6172,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -6131,20 +6186,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6153,75 +6208,75 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="23" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="49" fontId="8" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6230,22 +6285,28 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6582,7 +6643,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V97"/>
+  <dimension ref="A2:V102"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -6752,873 +6813,895 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="15"/>
+      <c r="B13" s="33" t="s">
+        <v>286</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-    </row>
-    <row r="14" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+    </row>
+    <row r="15" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B15" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C15" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+    <row r="16" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B16" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C16" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="13" t="s">
+    <row r="17" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
         <v>65</v>
-      </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="9"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="30" t="s">
-        <v>201</v>
       </c>
       <c r="B18" s="12"/>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="B19" s="12"/>
+      <c r="C19" s="9"/>
+    </row>
+    <row r="20" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B20" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C20" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="31" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-    </row>
-    <row r="21" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
       <c r="B21" s="15"/>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="15"/>
+    </row>
+    <row r="22" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="9"/>
-    </row>
-    <row r="23" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="B23" s="12"/>
+      <c r="C23" s="9"/>
+    </row>
+    <row r="24" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B24" s="12"/>
       <c r="C24" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="B25" s="12"/>
+      <c r="C25" s="13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B26" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="13"/>
-    </row>
-    <row r="26" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+      <c r="C26" s="13"/>
+    </row>
+    <row r="27" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B27" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C27" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="B27" s="13"/>
-      <c r="C27" s="13" t="s">
+    <row r="28" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="B28" s="13"/>
+      <c r="C28" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="216" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+    <row r="29" spans="1:4" ht="216" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B29" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C29" s="15" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="10" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="9"/>
-    </row>
-    <row r="30" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="12"/>
+      <c r="C30" s="9"/>
+    </row>
+    <row r="31" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B31" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C31" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="B31" s="12"/>
-      <c r="C31" s="13" t="s">
+    <row r="32" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="B32" s="12"/>
+      <c r="C32" s="13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+    <row r="33" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B33" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C33" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+    <row r="34" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13" t="s">
+      <c r="B34" s="13"/>
+      <c r="C34" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="B34" s="12"/>
-      <c r="C34" s="13" t="s">
+    <row r="35" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="B35" s="12"/>
+      <c r="C35" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B35" s="12"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="2"/>
-    </row>
-    <row r="36" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B37" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C37" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="B37" s="12"/>
-      <c r="C37" s="15" t="s">
+    <row r="38" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="B38" s="12"/>
+      <c r="C38" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+    <row r="39" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B39" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C39" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="D38" s="2"/>
-    </row>
-    <row r="39" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="B39" s="12"/>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="2"/>
+    </row>
+    <row r="40" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B40" s="12"/>
+      <c r="C40" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+    <row r="41" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B41" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C41" s="13" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="17" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="1" t="s">
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="B42" s="15" t="s">
+    <row r="43" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="B43" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C43" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D43" s="15" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="10" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="1" t="s">
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="1" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="216" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B44" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D44" s="42" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="216" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D45" s="42" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="216" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B46" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C46" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="D45" s="42" t="s">
+      <c r="D46" s="42" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="10" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="26" t="s">
+    <row r="48" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B48" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C48" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
+    <row r="49" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B49" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C49" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
+    <row r="50" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B50" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="C50" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="9" t="s">
+    <row r="51" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B50" s="15" t="s">
+      <c r="B51" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C51" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="4" t="s">
+    <row r="52" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B52" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C52" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="9" t="s">
+    <row r="53" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B53" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C53" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D53" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="15" t="s">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B54" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C54" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="D53" s="15"/>
-    </row>
-    <row r="54" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A54" s="15" t="s">
+      <c r="D54" s="15"/>
+    </row>
+    <row r="55" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C55" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="D54" s="15" t="s">
+      <c r="D55" s="15" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="15" t="s">
+    <row r="56" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B56" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="C56" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="D55" s="15" t="s">
+      <c r="D56" s="15" t="s">
         <v>179</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B58" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C58" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D58" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="9" t="s">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B59" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="C59" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D59" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A59" s="9" t="s">
+    <row r="60" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A60" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B59" s="15" t="s">
+      <c r="B60" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="C60" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="D59" s="15"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="10" t="s">
+      <c r="D60" s="15"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
-    </row>
-    <row r="61" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="C61" s="15" t="s">
+      <c r="B61" s="15"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
+    </row>
+    <row r="62" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C62" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="D61" s="15"/>
-    </row>
-    <row r="62" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="1" t="s">
+      <c r="D62" s="15"/>
+    </row>
+    <row r="63" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B63" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C63" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="D62" s="15"/>
-    </row>
-    <row r="63" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
+      <c r="D63" s="15"/>
+    </row>
+    <row r="64" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B64" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="C64" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="D63" s="15"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="10" t="s">
+      <c r="D64" s="15"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="B64" s="15"/>
-      <c r="C64" s="15"/>
-      <c r="D64" s="15" t="s">
+      <c r="B65" s="15"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="30" t="s">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="B65" s="12"/>
-      <c r="C65" s="9"/>
-    </row>
-    <row r="66" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
+      <c r="B66" s="12"/>
+      <c r="C66" s="9"/>
+    </row>
+    <row r="67" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B66" s="15" t="s">
+      <c r="B67" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="C66" s="15" t="s">
+      <c r="C67" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="31" t="s">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="B67" s="15"/>
-      <c r="C67" s="15"/>
-    </row>
-    <row r="68" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A68" s="2"/>
       <c r="B68" s="15"/>
-      <c r="C68" s="29" t="s">
+      <c r="C68" s="15"/>
+    </row>
+    <row r="69" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A69" s="2"/>
+      <c r="B69" s="15"/>
+      <c r="C69" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D69" s="2" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="10" t="s">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B69" s="15"/>
-      <c r="C69" s="15"/>
-      <c r="D69" s="1" t="s">
+      <c r="B70" s="15"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="1" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C70" s="29" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C71" s="29" t="s">
-        <v>221</v>
-      </c>
-      <c r="D71" s="2"/>
+        <v>214</v>
+      </c>
     </row>
     <row r="72" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C72" s="29" t="s">
+        <v>221</v>
+      </c>
+      <c r="D72" s="2"/>
+    </row>
+    <row r="73" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B72" s="29" t="s">
+      <c r="B73" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="C72" s="29" t="s">
+      <c r="C73" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
+    <row r="74" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B74" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C73" s="29" t="s">
+      <c r="C74" s="29" t="s">
         <v>227</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+    <row r="75" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B75" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C75" s="29" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
+    <row r="76" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B76" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C75" s="29" t="s">
+      <c r="C76" s="29" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A76" s="1" t="s">
+    <row r="77" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B77" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C76" s="32" t="s">
+      <c r="C77" s="32" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A77" s="1" t="s">
+    <row r="78" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B78" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C77" s="29" t="s">
+      <c r="C78" s="29" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="10" t="s">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D79" s="1" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C79" s="9"/>
-      <c r="D79" s="2"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C80" s="9"/>
+      <c r="D80" s="2"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="C81" s="9"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>236</v>
+        <v>253</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="C82" s="9"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C83" s="9"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C84" s="9"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C85" s="9"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>240</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="C86" s="9"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A88" s="32" t="s">
+    <row r="89" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A89" s="32" t="s">
         <v>247</v>
       </c>
-      <c r="B88" s="32"/>
-      <c r="C88" s="32" t="s">
+      <c r="B89" s="32"/>
+      <c r="C89" s="32" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A89" s="32" t="s">
+    <row r="90" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A90" s="32" t="s">
         <v>249</v>
       </c>
-      <c r="B89" s="32" t="s">
+      <c r="B90" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="C89" s="32" t="s">
+      <c r="C90" s="32" t="s">
         <v>250</v>
       </c>
-      <c r="D89" s="32" t="s">
+      <c r="D90" s="32" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A90" s="1" t="s">
+    <row r="91" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B90" s="32" t="s">
+      <c r="B91" s="32" t="s">
         <v>261</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="1" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A93" s="1" t="s">
+    <row r="94" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B93" s="32" t="s">
+      <c r="B94" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="C93" s="32" t="s">
+      <c r="C94" s="32" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="1" t="s">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B95" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C94" s="33" t="s">
+      <c r="C95" s="33" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="34" t="s">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="34" t="s">
         <v>258</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D96" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="1" t="s">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B97" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C96" s="32" t="s">
+      <c r="C97" s="32" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" s="1" t="s">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B98" s="2" t="s">
         <v>263</v>
       </c>
     </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="10" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="144" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C102" s="44" t="s">
+        <v>283</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -7663,10 +7746,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="43"/>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
+      <c r="A1" s="45"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="22"/>
@@ -8030,7 +8113,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C30:D44">
     <sortCondition ref="D30:D44"/>
   </sortState>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -8096,7 +8179,7 @@
     <row r="4" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="38"/>
       <c r="B4" s="38"/>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="43" t="s">
         <v>282</v>
       </c>
     </row>

--- a/4 четверть_9_JavaScript_Vue 3.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A1598B-45A4-45D4-A55C-982CA60106EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AA9107-EF8D-4D1D-B314-FA3DFC0BF592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="192" yWindow="-216" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="База" sheetId="12" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="290">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -2582,66 +2582,6 @@
   </si>
   <si>
     <t xml:space="preserve">Вариант 3 - стрелочная функция без return </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Пояснение - удобно!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Если мы опускаем return , значит внутри фигурных скобок уже </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>не стэк вызова функции</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>а сам object, который мы возвращаем в return</t>
-    </r>
   </si>
   <si>
     <t>data() { return {}}</t>
@@ -5851,17 +5791,179 @@
       <t>);</t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение - удобно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Если мы опускаем return , значит внутри фигурных скобок уже </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>не стэк вызова функции</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">а сам object, который мы возвращаем в return
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Важно - неудобно!</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Если в data есть обращение через this, то будет ошибка или не будет работать вообще! Так как this в стрелочной функции определяется в момент обращения к ней</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Не будет работать</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    data: () =&gt; ({
+        colorTypes: [{
+            value: 'notmo',
+            label</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: this.$t('noMoreThanDays')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+        }, {
+...
+        },
+    }),</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6172,10 +6274,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -6186,20 +6288,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6208,75 +6310,75 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="24" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="49" fontId="8" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6285,25 +6387,28 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6643,7 +6748,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V102"/>
+  <dimension ref="A2:V103"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -6767,7 +6872,7 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -6783,7 +6888,7 @@
         <v>55</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
@@ -6795,913 +6900,922 @@
         <v>156</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>159</v>
+      <c r="B12" s="47" t="s">
+        <v>287</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>155</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A13" s="15"/>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C13" s="47" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="15"/>
+      <c r="B14" s="33" t="s">
+        <v>285</v>
+      </c>
+      <c r="C14" s="45" t="s">
         <v>286</v>
       </c>
-      <c r="C13" s="46" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-    </row>
-    <row r="15" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+    </row>
+    <row r="16" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B16" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C16" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+    <row r="17" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B17" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C17" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="13" t="s">
+    <row r="18" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
         <v>65</v>
-      </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="9"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="30" t="s">
-        <v>201</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="9"/>
     </row>
-    <row r="20" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="9"/>
+    </row>
+    <row r="21" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B21" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="D20" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="31" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="31" t="s">
+        <v>201</v>
+      </c>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+    </row>
+    <row r="23" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-    </row>
-    <row r="22" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="29" t="s">
+      <c r="D23" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="9"/>
-    </row>
-    <row r="24" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="B24" s="12"/>
+      <c r="C24" s="9"/>
+    </row>
+    <row r="25" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B25" s="12"/>
       <c r="C25" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="B26" s="12"/>
+      <c r="C26" s="13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B27" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="C26" s="13"/>
-    </row>
-    <row r="27" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="C27" s="13"/>
+    </row>
+    <row r="28" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B28" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C28" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="B28" s="13"/>
-      <c r="C28" s="13" t="s">
+    <row r="29" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="B29" s="13"/>
+      <c r="C29" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="216" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+    <row r="30" spans="1:4" ht="216" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B30" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C30" s="15" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="10" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="9"/>
-    </row>
-    <row r="31" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="12"/>
+      <c r="C31" s="9"/>
+    </row>
+    <row r="32" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B32" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C32" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="B32" s="12"/>
-      <c r="C32" s="13" t="s">
+    <row r="33" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="B33" s="12"/>
+      <c r="C33" s="13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+    <row r="34" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B34" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C34" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+    <row r="35" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13" t="s">
+      <c r="B35" s="13"/>
+      <c r="C35" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="12"/>
-      <c r="C35" s="13" t="s">
+    <row r="36" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="B36" s="12"/>
+      <c r="C36" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="10" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="2"/>
-    </row>
-    <row r="37" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="B37" s="12"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B38" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C38" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="B38" s="12"/>
-      <c r="C38" s="15" t="s">
+    <row r="39" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="B39" s="12"/>
+      <c r="C39" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
+    <row r="40" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B40" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C40" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="D39" s="2"/>
-    </row>
-    <row r="40" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="B40" s="12"/>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2"/>
+    </row>
+    <row r="41" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B41" s="12"/>
+      <c r="C41" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+    <row r="42" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B42" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C42" s="13" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="17" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="1" t="s">
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="1" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="B43" s="15" t="s">
+    <row r="44" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="B44" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C44" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D44" s="15" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="10" t="s">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="1" t="s">
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="1" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="216" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B45" s="32" t="s">
-        <v>254</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D45" s="42" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="216" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B46" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D46" s="42" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="216" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B47" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C47" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="D46" s="42" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="10" t="s">
+      <c r="D47" s="42" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="26" t="s">
+    <row r="49" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B49" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="C50" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B49" s="15" t="s">
+      <c r="D50" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="C49" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" s="15" t="s">
+      <c r="C52" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="D52" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B52" s="2" t="s">
+      <c r="C53" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="D53" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C54" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="D53" s="2" t="s">
+      <c r="D54" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="15" t="s">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="15" t="s">
         <v>131</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="D54" s="15"/>
-    </row>
-    <row r="55" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="15" t="s">
-        <v>90</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C55" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="D55" s="15"/>
+    </row>
+    <row r="56" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D55" s="15" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A56" s="15" t="s">
+      <c r="C56" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C56" s="15" t="s">
+      <c r="B57" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D56" s="15" t="s">
+      <c r="C57" s="15" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A57" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>25</v>
+      <c r="D57" s="15" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A58" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B59" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="D61" s="15"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="B62" s="15"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="15"/>
+    </row>
+    <row r="63" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C63" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="D63" s="15"/>
+    </row>
+    <row r="64" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C64" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="D64" s="15"/>
+    </row>
+    <row r="65" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="D65" s="15"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="B67" s="12"/>
+      <c r="C67" s="9"/>
+    </row>
+    <row r="68" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B68" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="C58" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B60" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="C60" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="D60" s="15"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="B61" s="15"/>
-      <c r="C61" s="15"/>
-      <c r="D61" s="15"/>
-    </row>
-    <row r="62" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="C62" s="15" t="s">
-        <v>194</v>
-      </c>
-      <c r="D62" s="15"/>
-    </row>
-    <row r="63" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C63" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="D63" s="15"/>
-    </row>
-    <row r="64" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C64" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="D64" s="15"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="10" t="s">
+      <c r="C68" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="31" t="s">
+        <v>201</v>
+      </c>
+      <c r="B69" s="15"/>
+      <c r="C69" s="15"/>
+    </row>
+    <row r="70" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A70" s="2"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="B65" s="15"/>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="B66" s="12"/>
-      <c r="C66" s="9"/>
-    </row>
-    <row r="67" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B67" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="C67" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="31" t="s">
-        <v>202</v>
-      </c>
-      <c r="B68" s="15"/>
-      <c r="C68" s="15"/>
-    </row>
-    <row r="69" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A69" s="2"/>
-      <c r="B69" s="15"/>
-      <c r="C69" s="29" t="s">
-        <v>203</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15"/>
-      <c r="D70" s="1" t="s">
+      <c r="B71" s="15"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="1" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C71" s="29" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C72" s="29" t="s">
-        <v>221</v>
-      </c>
-      <c r="D72" s="2"/>
+        <v>213</v>
+      </c>
     </row>
     <row r="73" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C73" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="D73" s="2"/>
+    </row>
+    <row r="74" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B74" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="C74" s="29" t="s">
+        <v>221</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B73" s="29" t="s">
+      <c r="B75" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C73" s="29" t="s">
-        <v>222</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
+      <c r="C75" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C74" s="29" t="s">
+      <c r="B76" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C76" s="29" t="s">
         <v>227</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
+    </row>
+    <row r="77" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B77" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C77" s="29" t="s">
         <v>229</v>
       </c>
-      <c r="C75" s="29" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
+    </row>
+    <row r="78" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C78" s="32" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="C79" s="29" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="C76" s="29" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A77" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C77" s="32" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C78" s="29" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="10" t="s">
+      <c r="D80" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C80" s="9"/>
-      <c r="D80" s="2"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C81" s="9"/>
+      <c r="D81" s="2"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="C82" s="9"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="C83" s="9"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C84" s="9"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C85" s="9"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C86" s="9"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>240</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="C87" s="9"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A89" s="32" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A90" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="B90" s="32"/>
+      <c r="C90" s="32" t="s">
         <v>247</v>
       </c>
-      <c r="B89" s="32"/>
-      <c r="C89" s="32" t="s">
+    </row>
+    <row r="91" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A91" s="32" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A90" s="32" t="s">
+      <c r="B91" s="32" t="s">
+        <v>255</v>
+      </c>
+      <c r="C91" s="32" t="s">
         <v>249</v>
       </c>
-      <c r="B90" s="32" t="s">
+      <c r="D91" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="C90" s="32" t="s">
-        <v>250</v>
-      </c>
-      <c r="D90" s="32" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A91" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B91" s="32" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
+      </c>
+      <c r="B92" s="32" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B95" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="C95" s="32" t="s">
         <v>245</v>
       </c>
-      <c r="B94" s="32" t="s">
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C94" s="32" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B95" s="2" t="s">
+      <c r="C96" s="33" t="s">
         <v>243</v>
       </c>
-      <c r="C95" s="33" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="D96" s="1" t="s">
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="34" t="s">
+        <v>257</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="1" t="s">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B98" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C98" s="32" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C97" s="32" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="10" t="s">
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="10" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" ht="144" x14ac:dyDescent="0.3">
-      <c r="A102" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C102" s="44" t="s">
-        <v>283</v>
+      <c r="C103" s="44" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -7746,10 +7860,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="45"/>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
+      <c r="A1" s="46"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="22"/>
@@ -7979,13 +8093,13 @@
     </row>
     <row r="6" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B6" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>265</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="D6" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -7995,13 +8109,13 @@
     </row>
     <row r="8" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B8" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
@@ -8011,38 +8125,38 @@
     </row>
     <row r="10" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11" s="36" t="s">
         <v>273</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="288" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C13" s="36" t="s">
         <v>278</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.3">
@@ -8113,7 +8227,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C30:D44">
     <sortCondition ref="D30:D44"/>
   </sortState>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -8168,7 +8282,7 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B3" s="38"/>
       <c r="C3" s="37"/>
@@ -8180,7 +8294,7 @@
       <c r="A4" s="38"/>
       <c r="B4" s="38"/>
       <c r="C4" s="43" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">

--- a/4 четверть_9_JavaScript_Vue 3.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AA9107-EF8D-4D1D-B314-FA3DFC0BF592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E1E3B9-A8AA-48B2-B309-20F18B508861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="База" sheetId="12" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="291">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -2185,76 +2185,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">&lt;button 
-         v-bind:class="
-        {
-          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>'btn-danger': colorEdit &amp;&amp; baseSettings.editUserCurrentSetting,
-          'btn-default': !colorEdit || !baseSettings.editUserCurrentSetting, 
-          'btn-primary': colorEdit &amp;&amp; !baseSettings.editUserCurrentSetting</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-         }
-       "
-&lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;button 
-        v-bind:class="[
-           </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">'custom_class_1',
-            {'btn-danger': !colorEdit || !baseSettings.editUserCurrentSetting}, 
-           colorEdit &amp;&amp; baseSettings.editUserCurrentSetting ? 'btn-danger' : null </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-         ]"
-&lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
     <t>inline стили</t>
   </si>
   <si>
@@ -2331,34 +2261,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>&lt;button  v-bind:class="</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{'btn-danger': !colorEdit || !baseSettings.editUserCurrentSetting}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> "&gt; &lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
     <t>Подход 1</t>
   </si>
   <si>
@@ -2371,41 +2273,7 @@
     <t>несколько стилей</t>
   </si>
   <si>
-    <t>несколько стилей с условиями</t>
-  </si>
-  <si>
     <t>несколько стилей, комбинированных в объект</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;el-button </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:style="{
-  backgroundColor: item.length === 0 ? "#409EFF" : "#FFF", 
-  …
-}"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&gt; &lt;/el-button&gt;</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2436,69 +2304,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">  &gt; &lt;/el-button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;button  v-bind:class=" </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>colorEdit  ? 'btn-danger' : null</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> "&gt; &lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;button 
-         v-bind:class="
-        [
-          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">colorEdit ? 'btn-danger' : null ,
-          colorEdit ? 'btn-danger' : null </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-         ]
-       "
-&lt;/button&gt;</t>
     </r>
   </si>
   <si>
@@ -5945,17 +5750,455 @@
     }),</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;button  v-bind:class=" </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  ? 'btn-danger' : null</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> "&gt; &lt;/button&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;button 
+         v-bind:class="
+        [
+          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ? 'btn-danger' : null ,
+          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ? 'btn-danger' : null </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+         ]
+       "
+&lt;/button&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;button 
+         v-bind:class="
+        {
+          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">'btn-danger': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit &amp;&amp; baseSettings.editUserCurrentSetting</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,
+          'btn-default': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>!colorEdit || !baseSettings.editUserCurrentSetting</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, 
+          'btn-primary': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit &amp;&amp; !baseSettings.editUserCurrentSetting</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+         }
+       "
+&lt;/button&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;button 
+        v-bind:class="[
+           </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">'custom_class_1',
+            {'btn-danger': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>!colorEdit || !baseSettings.editUserCurrentSetting</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">}, 
+           </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit &amp;&amp; baseSettings.editUserCurrentSetting</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ? 'btn-danger' : null </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+         ]"
+&lt;/button&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;el-button </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:style="{
+  backgroundColor:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> item.length === 0</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ? "#409EFF" : "#FFF", 
+  …
+}"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&gt; &lt;/el-button&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>один class</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (самый предпочтительный)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>&lt;button  v-bind:class="</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">{'btn-danger': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>!colorEdit, ...</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> "&gt; &lt;/button&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">несколько стилей с условиями </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(самый предпочтительный)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6274,10 +6517,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -6288,20 +6531,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6310,75 +6553,72 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="24" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="25" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="49" fontId="9" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="49" fontId="10" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6387,19 +6627,25 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6408,7 +6654,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6872,7 +7118,7 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -6888,51 +7134,51 @@
         <v>55</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="15" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="B12" s="47" t="s">
-        <v>287</v>
+        <v>151</v>
+      </c>
+      <c r="B12" s="45" t="s">
+        <v>280</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A13" s="15"/>
-      <c r="B13" s="47" t="s">
-        <v>288</v>
-      </c>
-      <c r="C13" s="47" t="s">
-        <v>289</v>
+      <c r="B13" s="45" t="s">
+        <v>281</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="C14" s="45" t="s">
-        <v>286</v>
+        <v>278</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
@@ -6988,7 +7234,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="30" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="9"/>
@@ -6998,10 +7244,10 @@
         <v>101</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>66</v>
@@ -7009,7 +7255,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="31" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -7018,10 +7264,10 @@
       <c r="A23" s="2"/>
       <c r="B23" s="15"/>
       <c r="C23" s="29" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -7247,13 +7493,13 @@
         <v>126</v>
       </c>
       <c r="B46" s="32" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C46" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D46" s="42" t="s">
-        <v>254</v>
+      <c r="D46" s="41" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="216" x14ac:dyDescent="0.3">
@@ -7266,8 +7512,8 @@
       <c r="C47" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="D47" s="42" t="s">
-        <v>280</v>
+      <c r="D47" s="41" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -7283,10 +7529,10 @@
         <v>20</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>19</v>
@@ -7297,10 +7543,10 @@
         <v>17</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>21</v>
@@ -7311,10 +7557,10 @@
         <v>16</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>22</v>
@@ -7325,10 +7571,10 @@
         <v>9</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>23</v>
@@ -7339,10 +7585,10 @@
         <v>18</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>24</v>
@@ -7353,10 +7599,10 @@
         <v>14</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>28</v>
@@ -7367,10 +7613,10 @@
         <v>131</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D55" s="15"/>
     </row>
@@ -7379,13 +7625,13 @@
         <v>90</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
@@ -7393,13 +7639,13 @@
         <v>133</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -7407,10 +7653,10 @@
         <v>11</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>25</v>
@@ -7421,10 +7667,10 @@
         <v>12</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>27</v>
@@ -7435,10 +7681,10 @@
         <v>10</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>26</v>
@@ -7449,16 +7695,16 @@
         <v>13</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D61" s="15"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -7466,7 +7712,7 @@
     </row>
     <row r="63" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C63" s="15" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D63" s="15"/>
     </row>
@@ -7475,10 +7721,10 @@
         <v>131</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C64" s="29" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D64" s="15"/>
     </row>
@@ -7487,26 +7733,26 @@
         <v>90</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="D65" s="15"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="10" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
       <c r="D66" s="15" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="30" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B67" s="12"/>
       <c r="C67" s="9"/>
@@ -7516,10 +7762,10 @@
         <v>101</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>66</v>
@@ -7527,7 +7773,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="31" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
@@ -7536,15 +7782,15 @@
       <c r="A70" s="2"/>
       <c r="B70" s="15"/>
       <c r="C70" s="29" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="10" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
@@ -7554,229 +7800,229 @@
     </row>
     <row r="72" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C72" s="29" t="s">
         <v>206</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C72" s="29" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C73" s="29" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D73" s="2"/>
     </row>
     <row r="74" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B74" s="29" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C74" s="29" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C75" s="29" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C76" s="29" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C77" s="29" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C78" s="32" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C79" s="29" t="s">
         <v>212</v>
-      </c>
-      <c r="C79" s="29" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="10" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="2"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C82" s="9"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C83" s="9"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C84" s="9"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C85" s="9"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C86" s="9"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C87" s="9"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A90" s="32" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B90" s="32"/>
       <c r="C90" s="32" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A91" s="32" t="s">
+        <v>241</v>
+      </c>
+      <c r="B91" s="32" t="s">
         <v>248</v>
       </c>
-      <c r="B91" s="32" t="s">
-        <v>255</v>
-      </c>
       <c r="C91" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="D91" s="32" t="s">
         <v>249</v>
-      </c>
-      <c r="D91" s="32" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B92" s="32" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B95" s="32" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C95" s="32" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C96" s="33" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="34" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>30</v>
@@ -7787,10 +8033,10 @@
         <v>131</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C98" s="32" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -7798,24 +8044,24 @@
         <v>90</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="10" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C103" s="44" t="s">
-        <v>282</v>
+        <v>277</v>
+      </c>
+      <c r="C103" s="43" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -7860,10 +8106,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="46"/>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
+      <c r="A1" s="47"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="22"/>
@@ -7894,7 +8140,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="P4" s="19"/>
       <c r="U4" s="19"/>
@@ -7903,27 +8149,27 @@
     <row r="5" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>149</v>
+        <v>290</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>287</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>134</v>
@@ -7934,7 +8180,7 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="15"/>
@@ -7942,61 +8188,61 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>151</v>
+        <v>136</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>283</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>142</v>
+        <v>288</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>289</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>152</v>
+        <v>146</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>284</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>135</v>
+        <v>147</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>285</v>
       </c>
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>286</v>
       </c>
       <c r="D13" s="1"/>
     </row>
@@ -8005,10 +8251,10 @@
         <v>118</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>139</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -8093,13 +8339,13 @@
     </row>
     <row r="6" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B6" s="32" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -8109,13 +8355,13 @@
     </row>
     <row r="8" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B8" s="32" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
@@ -8125,38 +8371,38 @@
     </row>
     <row r="10" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>270</v>
+        <v>264</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>263</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>273</v>
+        <v>268</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>274</v>
+        <v>269</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="288" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>278</v>
+        <v>270</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.3">
@@ -8227,7 +8473,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C30:D44">
     <sortCondition ref="D30:D44"/>
   </sortState>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -8282,96 +8528,96 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="37"/>
+        <v>272</v>
+      </c>
+      <c r="B3" s="37"/>
+      <c r="C3" s="36"/>
       <c r="P3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="2"/>
     </row>
     <row r="4" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="38"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="43" t="s">
-        <v>281</v>
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="42" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="39"/>
+      <c r="A5" s="36"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="38"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
+      <c r="A6" s="36"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="39"/>
+      <c r="A7" s="36"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="38"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
+      <c r="A8" s="36"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" s="37"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="39"/>
+      <c r="A9" s="36"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="38"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="41"/>
+      <c r="A10" s="36"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="40"/>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="37"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="41"/>
+      <c r="A11" s="36"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="40"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="41"/>
+      <c r="A12" s="36"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="40"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="41"/>
+      <c r="A13" s="36"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="40"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="37"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="39"/>
+      <c r="A14" s="36"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="38"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
+      <c r="A15" s="36"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="38"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="39"/>
+      <c r="A16" s="36"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="38"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="39"/>
+      <c r="A17" s="36"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="38"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="39"/>
+      <c r="A18" s="36"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="38"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="39"/>
+      <c r="A19" s="36"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="38"/>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.3">
       <c r="C38" s="27" t="s">

--- a/4 четверть_9_JavaScript_Vue 3.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E1E3B9-A8AA-48B2-B309-20F18B508861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA3A827C-D1D3-4876-82CD-BE49EB0FD1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="База" sheetId="12" r:id="rId1"/>
@@ -5502,6 +5502,637 @@
         <scheme val="minor"/>
       </rPr>
       <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">        changeText(scope, e, type=false) {
+            let dataName = (!type) ? 'usersDataFilteredComp' : 'ipAndPassArray';
+            let res = this[dataName].map(i =&gt; ({...i}));
+            let index = scope.$index;
+            let prop = scope.column.property;
+            res[index][prop] = e.target ? e.target.value : e;
+            this[dataName] = res;
+        },</t>
+  </si>
+  <si>
+    <t>Reflection</t>
+  </si>
+  <si>
+    <t>Удобно!</t>
+  </si>
+  <si>
+    <t>Поверхностное копирование - удобно!</t>
+  </si>
+  <si>
+    <r>
+      <t>let res = this[dataName].map(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i =&gt; ({...i})</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение - удобно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Если мы опускаем return , значит внутри фигурных скобок уже </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>не стэк вызова функции</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">а сам object, который мы возвращаем в return
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Важно - неудобно!</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Если в data есть обращение через this, то будет ошибка или не будет работать вообще! Так как this в стрелочной функции определяется в момент обращения к ней</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Не будет работать</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    data: () =&gt; ({
+        colorTypes: [{
+            value: 'notmo',
+            label</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: this.$t('noMoreThanDays')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+        }, {
+...
+        },
+    }),</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;button  v-bind:class=" </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  ? 'btn-danger' : null</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> "&gt; &lt;/button&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;button 
+         v-bind:class="
+        [
+          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ? 'btn-danger' : null ,
+          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ? 'btn-danger' : null </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+         ]
+       "
+&lt;/button&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;button 
+         v-bind:class="
+        {
+          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">'btn-danger': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit &amp;&amp; baseSettings.editUserCurrentSetting</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,
+          'btn-default': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>!colorEdit || !baseSettings.editUserCurrentSetting</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, 
+          'btn-primary': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit &amp;&amp; !baseSettings.editUserCurrentSetting</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+         }
+       "
+&lt;/button&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;button 
+        v-bind:class="[
+           </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">'custom_class_1',
+            {'btn-danger': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>!colorEdit || !baseSettings.editUserCurrentSetting</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">}, 
+           </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit &amp;&amp; baseSettings.editUserCurrentSetting</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ? 'btn-danger' : null </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+         ]"
+&lt;/button&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;el-button </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:style="{
+  backgroundColor:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> item.length === 0</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ? "#409EFF" : "#FFF", 
+  …
+}"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&gt; &lt;/el-button&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>один class</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (самый предпочтительный)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>&lt;button  v-bind:class="</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">{'btn-danger': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>!colorEdit, ...</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> "&gt; &lt;/button&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">несколько стилей с условиями </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(самый предпочтительный)</t>
     </r>
   </si>
   <si>
@@ -5545,652 +6176,33 @@
         someMethod(event, index) {}
     },
     watch: {
-        someProperty(newVal, oldVal) {}
+       someProperty: {
+            handler(newVal, oldVal){
+            },
+            deep: true
+        }
     }
 });</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        changeText(scope, e, type=false) {
-            let dataName = (!type) ? 'usersDataFilteredComp' : 'ipAndPassArray';
-            let res = this[dataName].map(i =&gt; ({...i}));
-            let index = scope.$index;
-            let prop = scope.column.property;
-            res[index][prop] = e.target ? e.target.value : e;
-            this[dataName] = res;
-        },</t>
-  </si>
-  <si>
-    <t>Reflection</t>
-  </si>
-  <si>
-    <t>Удобно!</t>
-  </si>
-  <si>
-    <t>Поверхностное копирование - удобно!</t>
-  </si>
-  <si>
-    <r>
-      <t>let res = this[dataName].map(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>i =&gt; ({...i})</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>);</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Пояснение - удобно!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Если мы опускаем return , значит внутри фигурных скобок уже </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>не стэк вызова функции</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">а сам object, который мы возвращаем в return
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Важно - неудобно!</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Если в data есть обращение через this, то будет ошибка или не будет работать вообще! Так как this в стрелочной функции определяется в момент обращения к ней</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Не будет работать</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-    data: () =&gt; ({
-        colorTypes: [{
-            value: 'notmo',
-            label</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: this.$t('noMoreThanDays')</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-        }, {
-...
-        },
-    }),</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;button  v-bind:class=" </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>colorEdit</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  ? 'btn-danger' : null</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> "&gt; &lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;button 
-         v-bind:class="
-        [
-          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>colorEdit</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ? 'btn-danger' : null ,
-          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>colorEdit</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ? 'btn-danger' : null </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-         ]
-       "
-&lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;button 
-         v-bind:class="
-        {
-          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">'btn-danger': </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>colorEdit &amp;&amp; baseSettings.editUserCurrentSetting</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">,
-          'btn-default': </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>!colorEdit || !baseSettings.editUserCurrentSetting</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, 
-          'btn-primary': </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>colorEdit &amp;&amp; !baseSettings.editUserCurrentSetting</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-         }
-       "
-&lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;button 
-        v-bind:class="[
-           </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">'custom_class_1',
-            {'btn-danger': </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>!colorEdit || !baseSettings.editUserCurrentSetting</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">}, 
-           </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>colorEdit &amp;&amp; baseSettings.editUserCurrentSetting</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ? 'btn-danger' : null </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-         ]"
-&lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;el-button </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:style="{
-  backgroundColor:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> item.length === 0</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ? "#409EFF" : "#FFF", 
-  …
-}"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&gt; &lt;/el-button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>один class</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (самый предпочтительный)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>&lt;button  v-bind:class="</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">{'btn-danger': </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>!colorEdit, ...</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> "&gt; &lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">несколько стилей с условиями </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(самый предпочтительный)</t>
-    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6517,8 +6529,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -6531,20 +6543,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6553,72 +6565,72 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="26" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="49" fontId="10" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6627,19 +6639,19 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6654,15 +6666,15 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{141A142D-D8A7-43F9-B8D2-54AA311FA1CB}"/>
     <cellStyle name="Обычный 2 2" xfId="2" xr:uid="{6AED7C1E-16D4-4B27-9CDE-4556C8555CBE}"/>
   </cellStyles>
@@ -7153,8 +7165,8 @@
       <c r="A12" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="B12" s="45" t="s">
-        <v>280</v>
+      <c r="B12" s="44" t="s">
+        <v>279</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>148</v>
@@ -7165,20 +7177,20 @@
     </row>
     <row r="13" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A13" s="15"/>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="44" t="s">
+        <v>280</v>
+      </c>
+      <c r="C13" s="44" t="s">
         <v>281</v>
-      </c>
-      <c r="C13" s="45" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="33" t="s">
+        <v>277</v>
+      </c>
+      <c r="C14" s="43" t="s">
         <v>278</v>
-      </c>
-      <c r="C14" s="44" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
@@ -8049,19 +8061,19 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C103" s="43" t="s">
-        <v>275</v>
+        <v>276</v>
+      </c>
+      <c r="C103" s="42" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -8159,10 +8171,10 @@
     <row r="6" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C6" s="48" t="s">
-        <v>287</v>
+        <v>289</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>286</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -8193,8 +8205,8 @@
       <c r="B9" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C9" s="46" t="s">
-        <v>283</v>
+      <c r="C9" s="45" t="s">
+        <v>282</v>
       </c>
       <c r="D9" s="2"/>
     </row>
@@ -8203,10 +8215,10 @@
         <v>141</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C10" s="45" t="s">
         <v>288</v>
-      </c>
-      <c r="C10" s="46" t="s">
-        <v>289</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -8217,8 +8229,8 @@
       <c r="B11" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="46" t="s">
-        <v>284</v>
+      <c r="C11" s="45" t="s">
+        <v>283</v>
       </c>
       <c r="D11" s="2"/>
     </row>
@@ -8229,8 +8241,8 @@
       <c r="B12" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C12" s="46" t="s">
-        <v>285</v>
+      <c r="C12" s="45" t="s">
+        <v>284</v>
       </c>
       <c r="D12" s="1"/>
     </row>
@@ -8241,8 +8253,8 @@
       <c r="B13" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="46" t="s">
-        <v>286</v>
+      <c r="C13" s="45" t="s">
+        <v>285</v>
       </c>
       <c r="D13" s="1"/>
     </row>
@@ -8473,7 +8485,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C30:D44">
     <sortCondition ref="D30:D44"/>
   </sortState>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -8539,8 +8551,8 @@
     <row r="4" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="37"/>
       <c r="B4" s="37"/>
-      <c r="C4" s="42" t="s">
-        <v>274</v>
+      <c r="C4" s="48" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">

--- a/4 четверть_9_JavaScript_Vue 3.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA3A827C-D1D3-4876-82CD-BE49EB0FD1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F82D5B-CF90-439A-817C-ACCFBAD11887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="База" sheetId="12" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="291">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -5707,295 +5707,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">&lt;button  v-bind:class=" </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>colorEdit</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  ? 'btn-danger' : null</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> "&gt; &lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;button 
-         v-bind:class="
-        [
-          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>colorEdit</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ? 'btn-danger' : null ,
-          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>colorEdit</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ? 'btn-danger' : null </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-         ]
-       "
-&lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;button 
-         v-bind:class="
-        {
-          </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">'btn-danger': </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>colorEdit &amp;&amp; baseSettings.editUserCurrentSetting</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">,
-          'btn-default': </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>!colorEdit || !baseSettings.editUserCurrentSetting</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, 
-          'btn-primary': </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>colorEdit &amp;&amp; !baseSettings.editUserCurrentSetting</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-         }
-       "
-&lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">&lt;button 
-        v-bind:class="[
-           </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">'custom_class_1',
-            {'btn-danger': </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>!colorEdit || !baseSettings.editUserCurrentSetting</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">}, 
-           </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>colorEdit &amp;&amp; baseSettings.editUserCurrentSetting</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ? 'btn-danger' : null </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-         ]"
-&lt;/button&gt;</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">&lt;el-button </t>
     </r>
     <r>
@@ -6064,58 +5775,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> (самый предпочтительный)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>&lt;button  v-bind:class="</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">{'btn-danger': </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>!colorEdit, ...</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> "&gt; &lt;/button&gt;</t>
     </r>
   </si>
   <si>
@@ -6184,25 +5843,355 @@
     }
 });</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;button  :class=" </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  ? 'btn-danger' : null</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> "&gt; &lt;/button&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>&lt;button  :class="</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">{'btn-danger': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>!colorEdit, ...</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> "&gt; &lt;/button&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;button  :class="
+        [
+          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ? 'btn-danger' : null ,
+          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ? 'btn-danger' : null </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+         ]
+       "
+&lt;/button&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;button :class="
+        {
+          </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">'btn-danger': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit &amp;&amp; baseSettings.editUserCurrentSetting</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,
+          'btn-default': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>!colorEdit || !baseSettings.editUserCurrentSetting</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, 
+          'btn-primary': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit &amp;&amp; !baseSettings.editUserCurrentSetting</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+         }
+       "
+&lt;/button&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">&lt;button :class="[
+           </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">'custom_class_1',
+            {'btn-danger': </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>!colorEdit || !baseSettings.editUserCurrentSetting</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">}, 
+           </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>colorEdit &amp;&amp; baseSettings.editUserCurrentSetting</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ? 'btn-danger' : null </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+         ]"
+&lt;/button&gt;</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6529,8 +6518,8 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -6543,20 +6532,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6565,72 +6554,72 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="25" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="49" fontId="10" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="26" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6639,16 +6628,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6663,13 +6649,16 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8073,7 +8062,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -8118,10 +8107,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="47"/>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
+      <c r="A1" s="46"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="22"/>
@@ -8171,10 +8160,10 @@
     <row r="6" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>286</v>
+        <v>284</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>282</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -8205,56 +8194,52 @@
       <c r="B9" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C9" s="45" t="s">
-        <v>282</v>
+      <c r="C9" s="47" t="s">
+        <v>286</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="1"/>
+      <c r="B10" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C10" s="45" t="s">
-        <v>288</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="45" t="s">
-        <v>283</v>
+      <c r="C11" s="47" t="s">
+        <v>288</v>
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>141</v>
-      </c>
+    <row r="12" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C12" s="45" t="s">
-        <v>284</v>
+      <c r="C12" s="47" t="s">
+        <v>289</v>
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="45" t="s">
-        <v>285</v>
+      <c r="C13" s="47" t="s">
+        <v>290</v>
       </c>
       <c r="D13" s="1"/>
     </row>
@@ -8265,7 +8250,7 @@
       <c r="B14" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="48" t="s">
         <v>139</v>
       </c>
     </row>
@@ -8485,7 +8470,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C30:D44">
     <sortCondition ref="D30:D44"/>
   </sortState>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -8551,8 +8536,8 @@
     <row r="4" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="37"/>
       <c r="B4" s="37"/>
-      <c r="C4" s="48" t="s">
-        <v>290</v>
+      <c r="C4" s="45" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">

--- a/4 четверть_9_JavaScript_Vue 3.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F82D5B-CF90-439A-817C-ACCFBAD11887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53EF600-E01C-49F4-BBA6-ADDAF05981DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6195" yWindow="-16005" windowWidth="27525" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="База" sheetId="12" r:id="rId1"/>
     <sheet name="Vue Css" sheetId="13" r:id="rId2"/>
-    <sheet name="Теория" sheetId="14" r:id="rId3"/>
-    <sheet name="Vue blank template" sheetId="15" r:id="rId4"/>
+    <sheet name="Директивы" sheetId="16" r:id="rId3"/>
+    <sheet name="Теория" sheetId="14" r:id="rId4"/>
+    <sheet name="Vue blank template" sheetId="15" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="293">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -6181,17 +6182,38 @@
 &lt;/button&gt;</t>
     </r>
   </si>
+  <si>
+    <t>Кастомные директивы</t>
+  </si>
+  <si>
+    <t>directives: {
+    focus: {
+        beforeMount(el)      {},  // директиву связали с элементом (еще в виртуальном DOM)
+        mounted(el)  {},  // элемент вставлен в реальный DOM ⬅️ ТЫ ЗДЕСЬ
+        updated(el)    {},  // обновился компонент, но дочерние еще не обновились
+        unmounted(el)    {}   // директиву отвязали от элемента
+    }
+}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6518,10 +6540,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -6532,20 +6554,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6554,72 +6576,72 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="26" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="49" fontId="10" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6628,13 +6650,16 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6646,19 +6671,19 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7203,7 +7228,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>104</v>
       </c>
@@ -8062,7 +8087,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -8107,10 +8132,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="46"/>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
+      <c r="A1" s="48"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="22"/>
@@ -8162,7 +8187,7 @@
       <c r="B6" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="46" t="s">
         <v>282</v>
       </c>
       <c r="D6" s="2"/>
@@ -8194,7 +8219,7 @@
       <c r="B9" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="46" t="s">
         <v>286</v>
       </c>
       <c r="D9" s="2"/>
@@ -8204,7 +8229,7 @@
       <c r="B10" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="46" t="s">
         <v>287</v>
       </c>
       <c r="D10" s="2"/>
@@ -8216,7 +8241,7 @@
       <c r="B11" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="46" t="s">
         <v>288</v>
       </c>
       <c r="D11" s="2"/>
@@ -8226,7 +8251,7 @@
       <c r="B12" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="46" t="s">
         <v>289</v>
       </c>
       <c r="D12" s="1"/>
@@ -8238,7 +8263,7 @@
       <c r="B13" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="46" t="s">
         <v>290</v>
       </c>
       <c r="D13" s="1"/>
@@ -8250,7 +8275,7 @@
       <c r="B14" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="47" t="s">
         <v>139</v>
       </c>
     </row>
@@ -8264,6 +8289,120 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2A651A-02D2-4C6D-91FC-2CBD73190D44}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V38"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="G2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C3" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="36"/>
+      <c r="C5" s="49" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="C11" s="35"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="C12" s="35"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="C13" s="35"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C38" s="27"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30C41A25-38CA-486A-87ED-62C44A5DF611}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -8470,13 +8609,13 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C30:D44">
     <sortCondition ref="D30:D44"/>
   </sortState>
-  <phoneticPr fontId="18" type="noConversion"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08DE618A-9635-4194-B69D-D0533DA1C310}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>

--- a/4 четверть_9_JavaScript_Vue 3.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53EF600-E01C-49F4-BBA6-ADDAF05981DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCF1A51-FDA8-4BF7-84D7-EC453B1C324C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6195" yWindow="-16005" windowWidth="27525" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9765" yWindow="-17865" windowWidth="23250" windowHeight="12450" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="База" sheetId="12" r:id="rId1"/>
-    <sheet name="Vue Css" sheetId="13" r:id="rId2"/>
-    <sheet name="Директивы" sheetId="16" r:id="rId3"/>
-    <sheet name="Теория" sheetId="14" r:id="rId4"/>
-    <sheet name="Vue blank template" sheetId="15" r:id="rId5"/>
+    <sheet name="Теория" sheetId="14" r:id="rId2"/>
+    <sheet name="Vue blank template" sheetId="15" r:id="rId3"/>
+    <sheet name="Vue Css" sheetId="13" r:id="rId4"/>
+    <sheet name="import require" sheetId="17" r:id="rId5"/>
+    <sheet name="Директивы" sheetId="16" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="358">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -6195,17 +6196,1258 @@
     }
 }</t>
   </si>
+  <si>
+    <t>import</t>
+  </si>
+  <si>
+    <t>Ссылка</t>
+  </si>
+  <si>
+    <t>ES6 modules are used to access variables or functions in a module explicitly exported by the modules it imports.</t>
+  </si>
+  <si>
+    <t>Named exports</t>
+  </si>
+  <si>
+    <t>Default import / export</t>
+  </si>
+  <si>
+    <t>Named exports are used to export several values from a module.</t>
+  </si>
+  <si>
+    <t>export</t>
+  </si>
+  <si>
+    <t>// mathConstants.js
+export const pi = 3.14;
+export const exp = 2.7;
+export const alpha = 0.35;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">// myFile.js
+import { pi, exp } from './mathConstants.js'; // Named import -- destructuring-like syntax
+console.log(pi) // 3.14
+console.log(exp) // 2.7
+// mySecondFile.js
+import * as constants from './mathConstants.js'; // Inject all exported values into constants variable
+console.log(constants.pi) // 3.14
+console.log(constants.exp) // 2.7
+import { foo as bar } from 'myFile.js'; // foo is imported and injected into a new bar variable
+</t>
+  </si>
+  <si>
+    <t>Concerning the default export, there is only a single default export per module. A default export can be a function, a class, an object or anything else. This value is considered the "main" exported value since it will be the simplest to import</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">// coolNumber.js
+const </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ultimateNumber</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 42;
+export default </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ultimateNumber</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Правило!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> In order to use the export declaration in a source file, the file must be interpreted by the runtime as a module.</t>
+    </r>
+  </si>
+  <si>
+    <t>Export/Import</t>
+  </si>
+  <si>
+    <t>export let name1, name2;</t>
+  </si>
+  <si>
+    <t>import { name1, name2 } from "module-name";</t>
+  </si>
+  <si>
+    <t>export const name1 = 1, name2 = 2;</t>
+  </si>
+  <si>
+    <t>export function functionName() { /* … */ }</t>
+  </si>
+  <si>
+    <t>import { functionName } from "module-name";</t>
+  </si>
+  <si>
+    <t>export class ClassName { /* … */ }</t>
+  </si>
+  <si>
+    <t>import { ClassName } from "module-name";</t>
+  </si>
+  <si>
+    <t>export function* generatorFunctionName() { /* … */ }</t>
+  </si>
+  <si>
+    <t>import { generatorFunctionName } from "module-name";</t>
+  </si>
+  <si>
+    <t>export const { name1, name2: bar } = o;</t>
+  </si>
+  <si>
+    <t>import { name1, bar } from "module-name";</t>
+  </si>
+  <si>
+    <t>export const [ name1, name2 ] = array;</t>
+  </si>
+  <si>
+    <t>export { name1, name2 };</t>
+  </si>
+  <si>
+    <t>export { variable1 as name1, variable2 as name2 };</t>
+  </si>
+  <si>
+    <t>export { variable1 as "string name" };</t>
+  </si>
+  <si>
+    <t>import { "string name" as variable1 } from "module-name";</t>
+  </si>
+  <si>
+    <t>export { name1 as default };</t>
+  </si>
+  <si>
+    <r>
+      <t>import name1 from "module-name";</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFF9FAFB"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t> или </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFF9FAFB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>import { default as name1 } from "module-name";</t>
+    </r>
+  </si>
+  <si>
+    <t>Генератор</t>
+  </si>
+  <si>
+    <t>Класс</t>
+  </si>
+  <si>
+    <t>Функция</t>
+  </si>
+  <si>
+    <t>Деструктуризация + Алиас</t>
+  </si>
+  <si>
+    <t>Деструктуризация</t>
+  </si>
+  <si>
+    <t>Переменная</t>
+  </si>
+  <si>
+    <t>Переменная со значением</t>
+  </si>
+  <si>
+    <t>Объект проинициализированный</t>
+  </si>
+  <si>
+    <t>Объект проинициализированный + Алиас</t>
+  </si>
+  <si>
+    <t>Объект проинициализированный named-&gt;default</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Export/Import</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>только для Modules</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>export default</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> function main() {
+    console.log("Main function");
+}
+export const </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>helper1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = () =&gt; {};
+export const </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>helper2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = () =&gt; {};
+export const </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CONSTANT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = 42;
+export class </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HelperClass</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> {}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>main</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, { </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>helper1, helper2, CONSTANT, HelperClass</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> } from "./module.js";</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Правило! </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Export default </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Может быть только один на файл. Это как "лицо" модуля — то, что возвращается по умолчанию при импорте без фигурных скобок.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Общий подход представлен справа -&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Правило!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Для агрегированного импорта следует использовать *</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">// myFile.js
+import </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>anyName</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> from './coolNumber.js';
+// Default export,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>independently from its name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>automatically injected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> into number variable;
+console.log(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>anyName</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) // 42
+</t>
+    </r>
+  </si>
+  <si>
+    <t>module.exports/require</t>
+  </si>
+  <si>
+    <t>module.exports</t>
+  </si>
+  <si>
+    <t>require</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">class UserAuthMiddleware { … }
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>module.exports</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>new UserAuthMiddleware();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">class ElementAlreadyExistsException extends Error { … }
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>module.exports</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ElementAlreadyExistsException;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">const UserAuth = …
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">module.exports </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UserAuth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">const </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UserAuthMiddleware</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>require</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>('./authMiddleware/userAuthMiddleware.js');</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">const </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NoSuchElementException</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>require</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>('../customExceptions/noSuchElementException.js');</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">const </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UserAuth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>require</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>('./userAuth.js');</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>module.exports/require</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">только </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>не для Modules</t>
+    </r>
+  </si>
+  <si>
+    <t>index.js</t>
+  </si>
+  <si>
+    <t>const NoSuchElementException = require('./noSuchElementException.js');
+const FailedToInsertElementException = require('./failedToInsertElementException.js');
+const FailedToDeleteElementException = require('./failedToDeleteElementException.js');
+const FailedToUpdateElementException = require('./failedToUpdateElementException.js');
+const MissingFieldException = require('./missingFieldException.js');
+const MissingRequestJson = require('./missingRequestJson.js');
+module.exports = {
+    NoSuchElementException,
+    FailedToInsertElementException,
+    FailedToDeleteElementException,
+    FailedToUpdateElementException,
+    MissingFieldException,
+    MissingRequestJson
+};</t>
+  </si>
+  <si>
+    <r>
+      <t>src\i18n\Bases\Templates\</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TemplatesSortPopover</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">\en.js
+export default {
+    sort: 'Sort',
+    byCreationDate: 'by creation date',
+    byUpdateDate: 'by update date',
+    byRating: 'by rating',
+    byDragNDrop: 'Manual',
+}
+…
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import BasesEn from './en.js';
+import SettingsEn from './Settings/en.js';
+import FormatterxlsEn from './Settings/formatterxls/conditionformat/en.js'
+import PartitionEn from './Settings/Partition/en.js';
+import PartitionPopoverEn from './Settings/Partition/PartitionPopover/en.js';
+import </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TemplateSortPopoverEn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> from './Templates/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TemplatesSortPopover</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">/en.js';
+import TemplateItemEn from './Templates/TemplateItem/en.js';
+import MaxEditorEn from './Templates/TemplateItem/MaxEditor/en.js';
+export default {
+    ...BasesEn,
+    ...SettingsEn,
+    ...FormatterxlsEn,
+    ...PartitionEn,
+    ...PartitionPopoverEn,
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    ...TemplateSortPopoverEn,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    ...TemplateItemEn,
+    ...MaxEditorEn,
+};</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Преимущества!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Возможность 
+(1) множественного импорта 
+(2) из разных файлов 
+(3) без обращения к конкретной переменной</t>
+    </r>
+  </si>
+  <si>
+    <t>Итог</t>
+  </si>
+  <si>
+    <t>Начало</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import Bases from './Bases/indexen.js';
+import Profile from './profile/indexen.js';
+import Manage from './Manage/indexen.js';
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Примечание! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Если бы название было index, то можно было бы импортировать :
+import Bases from '.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/Bases';</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+import Profile from '</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>./profile';</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+import Manage from '.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/Manage';</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="40" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6460,6 +7702,65 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFF9FAFB"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFF9FAFB"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -6538,12 +7839,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -6554,20 +7856,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6576,72 +7878,72 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="27" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="28" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="49" fontId="12" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -6650,13 +7952,16 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -6668,26 +7973,36 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Гиперссылка" xfId="3" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{141A142D-D8A7-43F9-B8D2-54AA311FA1CB}"/>
     <cellStyle name="Обычный 2 2" xfId="2" xr:uid="{6AED7C1E-16D4-4B27-9CDE-4556C8555CBE}"/>
@@ -8087,7 +9402,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="19" type="noConversion"/>
+  <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -8095,6 +9410,429 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30C41A25-38CA-486A-87ED-62C44A5DF611}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="G2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="144" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="288" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C38" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B44" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C30:D44">
+    <sortCondition ref="D30:D44"/>
+  </sortState>
+  <phoneticPr fontId="20" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08DE618A-9635-4194-B69D-D0533DA1C310}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="G2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="B3" s="37"/>
+      <c r="C3" s="36"/>
+      <c r="P3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="45" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" s="36"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="38"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" s="36"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="36"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="38"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="36"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="36"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="38"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="36"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="36"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="40"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="36"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="40"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="36"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="40"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="36"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="38"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="36"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="38"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="36"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="38"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="36"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="38"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="36"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="38"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="36"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="38"/>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C38" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B41" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B42" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B44" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{031AACE7-BBB7-40D6-880D-BFAE2A5485BC}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -8132,10 +9870,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="48"/>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
+      <c r="A1" s="49"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="22"/>
@@ -8288,7 +10026,384 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B7CAD42-95E0-4E20-A7EA-DF3B831CFF68}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V35"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="46.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="G2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C3" s="52" t="s">
+        <v>334</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="51" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" s="51" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="51" t="s">
+        <v>337</v>
+      </c>
+      <c r="B8" s="51" t="s">
+        <v>335</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="51"/>
+      <c r="B9" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="51" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="51" t="s">
+        <v>338</v>
+      </c>
+      <c r="B23" s="51" t="s">
+        <v>300</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="B24" s="53" t="s">
+        <v>356</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>350</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A25" s="51" t="s">
+        <v>354</v>
+      </c>
+      <c r="B25" s="51" t="s">
+        <v>352</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>353</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A26" s="51"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="51"/>
+    </row>
+    <row r="27" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="5"/>
+      <c r="C27" s="6"/>
+      <c r="G27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="5"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="52" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A29" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="B29" s="51"/>
+      <c r="C29" s="51"/>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B32" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B33" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="B35" s="51" t="s">
+        <v>354</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" location="imports--exports" xr:uid="{5F2650EE-EC1A-4EB5-A54A-484006789CA4}"/>
+    <hyperlink ref="D4" r:id="rId2" xr:uid="{7D3863D0-674C-43DF-8581-E2D9E02F5CED}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2A651A-02D2-4C6D-91FC-2CBD73190D44}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -8350,7 +10465,7 @@
     </row>
     <row r="5" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A5" s="36"/>
-      <c r="C5" s="49" t="s">
+      <c r="C5" s="48" t="s">
         <v>292</v>
       </c>
     </row>
@@ -8395,429 +10510,6 @@
     </row>
     <row r="38" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C38" s="27"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30C41A25-38CA-486A-87ED-62C44A5DF611}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:V45"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.88671875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.6640625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="G2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="5"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="C3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B6" s="32" t="s">
-        <v>257</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>258</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="32" t="s">
-        <v>261</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>263</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="144" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="288" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C38" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B40" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B41" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B42" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B43" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B44" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B45" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C30:D44">
-    <sortCondition ref="D30:D44"/>
-  </sortState>
-  <phoneticPr fontId="19" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08DE618A-9635-4194-B69D-D0533DA1C310}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:V45"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.88671875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.6640625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="G2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="5"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="36"/>
-      <c r="P3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="45" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" s="36"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="38"/>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" s="36"/>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" s="36"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="38"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" s="36"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" s="36"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="38"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="40"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="40"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="40"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="36"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="38"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="36"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="36"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="36"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="38"/>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C38" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B40" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B41" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B42" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B43" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B44" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B45" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>48</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/4 четверть_9_JavaScript_Vue 3.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCF1A51-FDA8-4BF7-84D7-EC453B1C324C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9794A9BA-1E54-4A42-A560-03E899EDBFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9765" yWindow="-17865" windowWidth="23250" windowHeight="12450" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="База" sheetId="12" r:id="rId1"/>
-    <sheet name="Теория" sheetId="14" r:id="rId2"/>
-    <sheet name="Vue blank template" sheetId="15" r:id="rId3"/>
-    <sheet name="Vue Css" sheetId="13" r:id="rId4"/>
-    <sheet name="import require" sheetId="17" r:id="rId5"/>
+    <sheet name="import require" sheetId="17" r:id="rId1"/>
+    <sheet name="База" sheetId="12" r:id="rId2"/>
+    <sheet name="Теория" sheetId="14" r:id="rId3"/>
+    <sheet name="Vue blank template" sheetId="15" r:id="rId4"/>
+    <sheet name="Vue Css" sheetId="13" r:id="rId5"/>
     <sheet name="Директивы" sheetId="16" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="366">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -7429,17 +7429,360 @@
       <t>/Manage';</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">class UserAuthMiddleware { … }
+class Logger { … }
+const config = { apiKey: "123" };
+const VERSION = "1.0.0";
+module.exports = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{
+    UserAuthMiddleware,  // Экспортируем сам класс
+    userAuthMiddleware: new UserAuthMiddleware(), // Экспортируем экземпляр
+    Logger,
+    logger: new Logger(),
+    config,
+    VERSION
+};</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Вариант 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+const { </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>userAuthMiddleware, config, VERSION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> } = require('./module');
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Вариант 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+const </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>myModule</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = require('./module');
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>myModule</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.userAuthMiddleware.doSomething();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">экспорт </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> констант</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">экспорт </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> константы</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>// Использование:
+const {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> userAuthMiddleware, Logger, config</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> } = require('./module');</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">class UserAuthMiddleware { … }
+class Logger { … }
+const config = { apiKey: "123" };
+// Не заменяем exports, а добавляем свойства
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">module.exports.userAuthMiddleware = new UserAuthMiddleware();
+module.exports.Logger = Logger;
+module.exports.config = config;
+module.exports.VERSION = "1.0.0";
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+// Короткая запись:
+// exports.userAuthMiddleware = new UserAuthMiddleware();
+// exports.Logger = Logger;
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>// Использование:
+const [</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>auth, logger, config</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>] = require('./module');</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>class UserAuthMiddleware { … }
+class Logger { … }
+module.exports =</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> [
+    new UserAuthMiddleware(),
+    new Logger(),
+    { apiKey: "123" }
+];</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="40" x14ac:knownFonts="1">
+  <fonts count="44" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -7761,6 +8104,24 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -7841,11 +8202,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -7856,20 +8217,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -7878,72 +8239,72 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="28" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="49" fontId="12" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="29" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="30" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="49" fontId="14" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -7952,13 +8313,19 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -7967,38 +8334,38 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -8331,6 +8698,425 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B7CAD42-95E0-4E20-A7EA-DF3B831CFF68}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V38"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="46.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="G2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C3" s="51" t="s">
+        <v>334</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>294</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="50" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="31" t="s">
+        <v>297</v>
+      </c>
+      <c r="B6" s="50"/>
+      <c r="C6" s="50" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="50" t="s">
+        <v>337</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="50"/>
+      <c r="B9" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="50" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="50" t="s">
+        <v>338</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>300</v>
+      </c>
+      <c r="C23" s="50" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="B24" s="52" t="s">
+        <v>356</v>
+      </c>
+      <c r="C24" s="52" t="s">
+        <v>350</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A25" s="50" t="s">
+        <v>354</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>352</v>
+      </c>
+      <c r="C25" s="50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A26" s="50"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="50"/>
+    </row>
+    <row r="27" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="5"/>
+      <c r="C27" s="6"/>
+      <c r="G27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="5"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="51" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A29" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="54" t="s">
+        <v>361</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="54" t="s">
+        <v>361</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="54" t="s">
+        <v>361</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C33" s="50" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="54" t="s">
+        <v>360</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C34" s="53" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="54" t="s">
+        <v>360</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C35" s="53" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="54" t="s">
+        <v>360</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="C37" s="52" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="B38" s="50" t="s">
+        <v>354</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" location="imports--exports" xr:uid="{5F2650EE-EC1A-4EB5-A54A-484006789CA4}"/>
+    <hyperlink ref="D4" r:id="rId2" xr:uid="{7D3863D0-674C-43DF-8581-E2D9E02F5CED}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE2ADE5-9A6F-4274-9C48-F960B495367E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -8543,7 +9329,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>104</v>
       </c>
@@ -9402,14 +10188,14 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="20" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30C41A25-38CA-486A-87ED-62C44A5DF611}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -9616,13 +10402,13 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C30:D44">
     <sortCondition ref="D30:D44"/>
   </sortState>
-  <phoneticPr fontId="20" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08DE618A-9635-4194-B69D-D0533DA1C310}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -9832,7 +10618,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{031AACE7-BBB7-40D6-880D-BFAE2A5485BC}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -9870,10 +10656,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="49"/>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
+      <c r="A1" s="55"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="22"/>
@@ -10023,383 +10809,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B7CAD42-95E0-4E20-A7EA-DF3B831CFF68}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:V35"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="46.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.88671875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.6640625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="G2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="5"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="C3" s="52" t="s">
-        <v>334</v>
-      </c>
-      <c r="D3" s="50" t="s">
-        <v>294</v>
-      </c>
-      <c r="P3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="34" t="s">
-        <v>305</v>
-      </c>
-      <c r="D4" s="50" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="51" t="s">
-        <v>304</v>
-      </c>
-      <c r="C5" s="51" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="31" t="s">
-        <v>297</v>
-      </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="34" t="s">
-        <v>299</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="51" t="s">
-        <v>337</v>
-      </c>
-      <c r="B8" s="51" t="s">
-        <v>335</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" s="51"/>
-      <c r="B9" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="31" t="s">
-        <v>296</v>
-      </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="51" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="34" t="s">
-        <v>299</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B21" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="51" t="s">
-        <v>338</v>
-      </c>
-      <c r="B23" s="51" t="s">
-        <v>300</v>
-      </c>
-      <c r="C23" s="51" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A24" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="B24" s="53" t="s">
-        <v>356</v>
-      </c>
-      <c r="C24" s="53" t="s">
-        <v>350</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A25" s="51" t="s">
-        <v>354</v>
-      </c>
-      <c r="B25" s="51" t="s">
-        <v>352</v>
-      </c>
-      <c r="C25" s="51" t="s">
-        <v>353</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A26" s="51"/>
-      <c r="B26" s="51"/>
-      <c r="C26" s="51"/>
-    </row>
-    <row r="27" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="5"/>
-      <c r="C27" s="6"/>
-      <c r="G27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
-      <c r="T27" s="28"/>
-      <c r="U27" s="5"/>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="51"/>
-      <c r="C28" s="52" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A29" s="34" t="s">
-        <v>340</v>
-      </c>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="34" t="s">
-        <v>341</v>
-      </c>
-      <c r="C30" s="34" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B31" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B32" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B33" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="C33" s="51" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="C34" s="53" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="B35" s="51" t="s">
-        <v>354</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" location="imports--exports" xr:uid="{5F2650EE-EC1A-4EB5-A54A-484006789CA4}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{7D3863D0-674C-43DF-8581-E2D9E02F5CED}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
 </worksheet>
 </file>
 

--- a/4 четверть_9_JavaScript_Vue 3.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9794A9BA-1E54-4A42-A560-03E899EDBFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C2DA9B-D846-4F99-A0C0-4701C85766F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="import require" sheetId="17" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="367">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -6200,9 +6200,6 @@
     <t>import</t>
   </si>
   <si>
-    <t>Ссылка</t>
-  </si>
-  <si>
     <t>ES6 modules are used to access variables or functions in a module explicitly exported by the modules it imports.</t>
   </si>
   <si>
@@ -7755,6 +7752,12 @@
     { apiKey: "123" }
 ];</t>
     </r>
+  </si>
+  <si>
+    <t>Ссылка - github</t>
+  </si>
+  <si>
+    <t>Ссылка - mdn</t>
   </si>
 </sst>
 </file>
@@ -8746,10 +8749,10 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C3" s="51" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>294</v>
+        <v>365</v>
       </c>
       <c r="P3" s="1"/>
       <c r="U3" s="1"/>
@@ -8757,34 +8760,34 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="34" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D4" s="49" t="s">
-        <v>294</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="50" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="31" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B6" s="50"/>
       <c r="C6" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="34" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C7" s="34" t="s">
         <v>293</v>
@@ -8792,37 +8795,37 @@
     </row>
     <row r="8" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A8" s="50" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B8" s="50" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" s="50" t="s">
         <v>335</v>
-      </c>
-      <c r="C8" s="50" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="50"/>
       <c r="B9" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="31" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B10" s="32"/>
       <c r="C10" s="50" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="34" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C11" s="34" t="s">
         <v>293</v>
@@ -8830,159 +8833,159 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A23" s="50" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B23" s="50" t="s">
+        <v>299</v>
+      </c>
+      <c r="C23" s="50" t="s">
         <v>300</v>
-      </c>
-      <c r="C23" s="50" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B24" s="52" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A25" s="50" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B25" s="50" t="s">
+        <v>351</v>
+      </c>
+      <c r="C25" s="50" t="s">
         <v>352</v>
       </c>
-      <c r="C25" s="50" t="s">
-        <v>353</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
@@ -9005,12 +9008,12 @@
       <c r="A28" s="2"/>
       <c r="B28" s="50"/>
       <c r="C28" s="51" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="34" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B29" s="50"/>
       <c r="C29" s="50"/>
@@ -9018,98 +9021,98 @@
     <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="C30" s="34" t="s">
         <v>341</v>
-      </c>
-      <c r="C30" s="34" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="54" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="54" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="54" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C33" s="50" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A34" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C34" s="53" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A35" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C35" s="53" t="s">
         <v>358</v>
-      </c>
-      <c r="C35" s="53" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A36" s="54" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C36" s="53" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C37" s="52" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
       <c r="B38" s="50" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" location="imports--exports" xr:uid="{5F2650EE-EC1A-4EB5-A54A-484006789CA4}"/>
-    <hyperlink ref="D4" r:id="rId2" xr:uid="{7D3863D0-674C-43DF-8581-E2D9E02F5CED}"/>
+    <hyperlink ref="D3" r:id="rId1" location="imports--exports" display="Ссылка" xr:uid="{5F2650EE-EC1A-4EB5-A54A-484006789CA4}"/>
+    <hyperlink ref="D4" r:id="rId2" display="Ссылка" xr:uid="{7D3863D0-674C-43DF-8581-E2D9E02F5CED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>

--- a/4 четверть_9_JavaScript_Vue 3.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C2DA9B-D846-4F99-A0C0-4701C85766F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959F8194-A9B2-4062-B3A2-7819E8419454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="-216" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="import require" sheetId="17" r:id="rId1"/>
     <sheet name="База" sheetId="12" r:id="rId2"/>
     <sheet name="Теория" sheetId="14" r:id="rId3"/>
-    <sheet name="Vue blank template" sheetId="15" r:id="rId4"/>
-    <sheet name="Vue Css" sheetId="13" r:id="rId5"/>
-    <sheet name="Директивы" sheetId="16" r:id="rId6"/>
+    <sheet name="Vue Css" sheetId="13" r:id="rId4"/>
+    <sheet name="Директивы" sheetId="16" r:id="rId5"/>
+    <sheet name="Vue blank template" sheetId="15" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="368">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -7758,6 +7758,9 @@
   </si>
   <si>
     <t>Ссылка - mdn</t>
+  </si>
+  <si>
+    <t>VUE 2</t>
   </si>
 </sst>
 </file>
@@ -10412,6 +10415,314 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{031AACE7-BBB7-40D6-880D-BFAE2A5485BC}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:V14"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="19" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="20" customWidth="1"/>
+    <col min="3" max="3" width="100.44140625" style="20" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="19" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="18" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="20" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="19" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="19" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="18" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="19" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="19" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="19" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="18" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="20" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="20" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="20" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="19" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="21"/>
+    <col min="21" max="21" width="67.77734375" style="20" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="19" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="19" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="19" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="19" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="19" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A1" s="55"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="U2" s="23"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C3" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="P3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="20"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="P4" s="19"/>
+      <c r="U4" s="19"/>
+      <c r="V4" s="20"/>
+    </row>
+    <row r="5" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>282</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>286</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>287</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>288</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>289</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>290</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:22" ht="216" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>139</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2A651A-02D2-4C6D-91FC-2CBD73190D44}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V38"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.88671875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.6640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="G2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="C3" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="36"/>
+      <c r="C5" s="48" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="C11" s="35"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="C12" s="35"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="C13" s="35"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C38" s="27"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08DE618A-9635-4194-B69D-D0533DA1C310}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -10469,7 +10780,9 @@
       <c r="V3" s="2"/>
     </row>
     <row r="4" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
+      <c r="A4" s="37" t="s">
+        <v>367</v>
+      </c>
       <c r="B4" s="37"/>
       <c r="C4" s="45" t="s">
         <v>285</v>
@@ -10619,312 +10932,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{031AACE7-BBB7-40D6-880D-BFAE2A5485BC}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:V14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36" style="19" customWidth="1"/>
-    <col min="2" max="2" width="50.5546875" style="20" customWidth="1"/>
-    <col min="3" max="3" width="100.44140625" style="20" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="18" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="20" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="19" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="19" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="18" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="19" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="19" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="19" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="19" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="18" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="20" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="20" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="20" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="19" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="21"/>
-    <col min="21" max="21" width="67.77734375" style="20" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="19" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="19" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="19" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="19" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="19" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="19"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="55"/>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="U2" s="23"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="C3" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="P3" s="19"/>
-      <c r="U3" s="19"/>
-      <c r="V3" s="20"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="P4" s="19"/>
-      <c r="U4" s="19"/>
-      <c r="V4" s="20"/>
-    </row>
-    <row r="5" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>282</v>
-      </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C9" s="46" t="s">
-        <v>286</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C10" s="46" t="s">
-        <v>287</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C11" s="46" t="s">
-        <v>288</v>
-      </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C13" s="46" t="s">
-        <v>290</v>
-      </c>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:22" ht="216" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C14" s="47" t="s">
-        <v>139</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2A651A-02D2-4C6D-91FC-2CBD73190D44}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:V38"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="62.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.44140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.5546875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.88671875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="56.88671875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.6640625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="67.6640625" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.44140625" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.44140625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.5546875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.33203125" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.6640625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="G2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="5"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="C3" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="P3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="34" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="36"/>
-      <c r="C5" s="48" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="C11" s="35"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="C12" s="35"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="C13" s="35"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-    </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C38" s="27"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
 </file>
--- a/4 четверть_9_JavaScript_Vue 3.xlsx
+++ b/4 четверть_9_JavaScript_Vue 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959F8194-A9B2-4062-B3A2-7819E8419454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60DCBF3E-F23F-4C64-9750-861AC145BB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="-216" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10335" yWindow="-15855" windowWidth="23250" windowHeight="12450" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="import require" sheetId="17" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="413">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -315,60 +315,6 @@
   </si>
   <si>
     <t>00 49 00</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">app.js
-Vue.createApp({
- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>//настройки приложения</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-}).mount(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>'#app'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
   </si>
   <si>
     <t>mount('#app')</t>
@@ -5063,153 +5009,10 @@
     <t>Достаточно инициировать свойство template</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Virtial DOM - то, что является основой vue.
-Все фреймворки решают одну проблему - оптимизацию общения javascript и dom дерева
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Преимущества Virtual Dom! </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Позволяет отрисовывать только один измененный элемент dom, а не весь блок целиком (что раньше делали более старые фреймворки Backbone, Marionet)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Фреймворки, использующие эту концепцию! </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Vue, React 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Фреймворки, использующие другую концепцию!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Angular</t>
-    </r>
-  </si>
-  <si>
     <t>Virtual DoM</t>
   </si>
   <si>
     <t>Доступ к Virtual DOM</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">app.js
-const h = Vue.h
-Vue.createApp({
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> render() {
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  return h('название тэга', {class: 'card center'}, 'This is text content')
-}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-}).mount(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>'#app'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -7762,17 +7565,1317 @@
   <si>
     <t>VUE 2</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Virtial DOM - то, что является основой vue.
+Все фреймворки решают одну проблему - оптимизацию общения javascript и dom дерева
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Важно для понимания! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Когда мы пишем код HTML в &lt;template&gt; мы не саму верстку описываем как в нативном подходе, а передаем ее Vue для преобразования в JS код в точности как тот, что представлен ниже. Далее ориентируясь по этому коду создается Virual DOM, который позволяет добить следующих преимуществ.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Преимущества Virtual Dom! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Позволяет отрисовывать только один измененный элемент dom, а не весь блок целиком (что раньше делали более старые фреймворки Backbone, Marionet)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Фреймворки, использующие эту концепцию! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Vue, React 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Фреймворки, использующие другую концепцию!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Angular
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Есть объект data, а есть this, который дает доступ ко всем свойствам data. Почему мы не обращеамся через data. Потому что VUE оборачивает объект data в proxy, чтобы добиться преимуществ реактивности.</t>
+    </r>
+  </si>
+  <si>
+    <t>03 16 00</t>
+  </si>
+  <si>
+    <t>Пояснение как реализуется реактивность</t>
+  </si>
+  <si>
+    <t>let title = 'Vue 3';
+let message = 'Заголовок это: ' + title;
+console.log(message); //Заголовок это: Vue 3
+title = 'Angular 10';
+console.log(message); //Заголовок это: Vue 3</t>
+  </si>
+  <si>
+    <t>В нативном JS отсутствует реактивность. Инициализация переменной от значения в другой переменной происходит один раз.</t>
+  </si>
+  <si>
+    <t>Нативный JS</t>
+  </si>
+  <si>
+    <t>Реактивность</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">const </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = {
+    title: 'Vue 3',
+    message: 'Заголовок это: Vue 3'
+}
+const proxy = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>new Proxy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(data, {
+    // get(target, p){ //не нужен
+    //     console.log(target);
+    //     console.log(p);
+    // },
+    set(target, key, value){
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>target[key] = value; //присваиваем значение самому свойству</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>if (key === 'title') {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>//присваиваем значения все зависимым свойствам</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+            target.message = 'Заголовок это: ' + value;
+        }
+        console.log(target);
+        console.log(key);
+        console.log(value);
+    }
+})
+proxy.title = 'Angular 10';
+console.log(proxy); //выведет объект data</t>
+    </r>
+  </si>
+  <si>
+    <t>`https://developer.mozilla.org/ru/docs/Web/JavaScript/Reference/Global_Objects/Proxy</t>
+  </si>
+  <si>
+    <t>Объект Proxy позволяет создать прокси для другого объекта, может перехватывать и переопределить основные операции для данного объекта.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">app.js
+const h = Vue.h
+Vue.createApp({
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> render() {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  return h('название тэга', {class: 'card center'}, 'This is text content')
+}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+}).mount(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'#app'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Используется специальный метод render()</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ render() {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  return h('название тэга', {class: 'card center'}, 'This is text content')
+}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">export default {
+  data() {
+    return {
+      message: 'Hello, Vue!'
+    };
+  },
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  beforeUpdate() {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    console.log('beforeUpdate');
+  },
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  updated() {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    console.log('updated');
+  },</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">export default {
+  data() {
+    return {
+      message: 'Hello, Vue!'
+    };
+  },
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  beforeCreate() { </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> //VirtaulDom отсутствует</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    console.log('beforeCreate');
+  },
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  created() {  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>//VirtaulDom отсутствует</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    console.log('created');
+  },
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  beforeMount() {</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> //VirtaulDom отсутствует</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    console.log('beforeMount');
+  },
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  mounted() { </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>//VirtaulDom создано</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    console.log('mounted');
+  },</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">export default {
+  data() {
+    return {
+      message: 'Hello, Vue!'
+    };
+  },
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  beforeUnmount() {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    console.log('unmounted');
+  },
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  unmounted() {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    console.log('unmounted');
+  },
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  errorCaptured(err, vm, info) {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+    console.error('Error captured:', err, info);
+  }
+};</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Полезно - удобно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> App.unmount() - уничтожить компонент</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">app.js
+Vue.createApp({
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>//настройки приложения
+  data() {
+    return {
+      title: "Это мое приложение"
+    }
+  }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+}).mount(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'#app'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">app.js
+Vue.createApp({
+ //настройки приложения
+  data() {
+    return {
+      title: "Это мое приложение 1"
+    }
+  }
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>}).mount('#app')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Vue.createApp({
+ //настройки приложения
+  data() {
+    return {
+      titleApp2: "Это мое приложение 2"
+    }
+  }
+}).mount(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>'#app2')</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">index.html
+&lt;div id="app"&gt; 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    &lt;h1&gt;{{title}}&lt;/h1&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&lt;/div&gt; 
+&lt;div id="app2"&gt; 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">    &lt;h1&gt;{{titleApp2}}&lt;/h1&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+&lt;/div&gt; </t>
+    </r>
+  </si>
+  <si>
+    <t>Работа с CLI - более простая установка проекта</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Создать проект vite + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vue3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Очень важно! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Данный вариант сработает только при node.js более 20.19+ or 22.12+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Рекомендованный вариант!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> опция для vue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Вариант без названия проекта - прямо в текущей директории!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> You can use </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for the project name to scaffold in the current directory.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">npm create vite@latest </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>my-vue-app</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>--</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> --template </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vue</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Важно! </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">npm 7+, extra double-dash is needed
+</t>
+    </r>
+  </si>
+  <si>
+    <t>03 43 00
+Стандартный мануал - https://vuejs.org/guide/quick-start.html#creating-a-vue-application</t>
+  </si>
+  <si>
+    <t>Папка public</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Хранит index.html, в котором инициализируется id = "app"
+</t>
+    </r>
+  </si>
+  <si>
+    <t>[*.{js,jsx,ts,tsx,vue}]
+indent_style = space
+indent_size = 2
+trim_trailing_whitespace = true
+insert_final_newline = true</t>
+  </si>
+  <si>
+    <t>Папка src/assets</t>
+  </si>
+  <si>
+    <t>Папка src/components -&gt; main.js</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Пояснение!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Для хранения изображений
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">import { createApp} from 'vue'
+import App from './App.vue'
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>createApp(App).mount('#app')</t>
+    </r>
+  </si>
+  <si>
+    <t>Папка src/components -&gt; App.vue</t>
+  </si>
+  <si>
+    <t>`https://github.com/vuejs/create-vue</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">npm </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>create vue@latest</t>
+    </r>
+  </si>
+  <si>
+    <t>Вариант 3 (устаревший - без vite)</t>
+  </si>
+  <si>
+    <t>`https://cli.vuejs.org/guide/installation.html</t>
+  </si>
+  <si>
+    <t>npm install -g @vue/cli
+npm update -g @vue/cli
+vue create hello-world   //vue create --help</t>
+  </si>
+  <si>
+    <t>Вариант 4 (GUI)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vue ui
+</t>
+  </si>
+  <si>
+    <t>Папка src -&gt; .editorconfig</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Создать проект </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vue3</t>
+    </r>
+  </si>
+  <si>
+    <t>04 04 00
+`https://cli.vuejs.org/guide/creating-a-project.html#using-the-gui</t>
+  </si>
+  <si>
+    <t>Полезный плагин для vscode</t>
+  </si>
+  <si>
+    <t>Vetur</t>
+  </si>
+  <si>
+    <t>04 10 00</t>
+  </si>
+  <si>
+    <t>(Обязательный) Позволяет понимать VsCode фреймворк Vue 3</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="44" x14ac:knownFonts="1">
+  <fonts count="47" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -8128,8 +9231,17 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8196,6 +9308,12 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -8208,11 +9326,11 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -8223,20 +9341,20 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -8245,72 +9363,72 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="30" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="49" fontId="14" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="31" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="32" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="49" fontId="16" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="9" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="11" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -8319,13 +9437,19 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -8334,44 +9458,53 @@
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="32" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="32" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -8431,6 +9564,99 @@
         <a:xfrm>
           <a:off x="6103768" y="814293"/>
           <a:ext cx="2636820" cy="1309679"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>72390</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>108198</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>5048701</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1392180</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3669A747-DEE2-447B-B2A7-80DDA06442CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6854190" y="28826073"/>
+          <a:ext cx="4964881" cy="1272552"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>95249</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>48611</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2571750</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>818638</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Рисунок 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28E93F2C-1B62-493E-9522-B257F2EF4FB6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6877049" y="30414311"/>
+          <a:ext cx="2476501" cy="785267"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8752,10 +9978,10 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C3" s="51" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="P3" s="1"/>
       <c r="U3" s="1"/>
@@ -8763,232 +9989,232 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="34" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D4" s="49" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="50" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="31" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B6" s="50"/>
       <c r="C6" s="50" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="34" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A8" s="50" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="50"/>
       <c r="B9" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="31" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B10" s="32"/>
       <c r="C10" s="50" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="34" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B21" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A23" s="50" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B23" s="50" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B24" s="52" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A25" s="50" t="s">
+        <v>350</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>348</v>
+      </c>
+      <c r="C25" s="50" t="s">
+        <v>349</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="B25" s="50" t="s">
-        <v>351</v>
-      </c>
-      <c r="C25" s="50" t="s">
-        <v>352</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
@@ -9011,12 +10237,12 @@
       <c r="A28" s="2"/>
       <c r="B28" s="50"/>
       <c r="C28" s="51" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="34" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B29" s="50"/>
       <c r="C29" s="50"/>
@@ -9024,92 +10250,92 @@
     <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="34" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="54" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="54" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="54" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C33" s="50" t="s">
         <v>343</v>
-      </c>
-      <c r="C33" s="50" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A34" s="54" t="s">
+        <v>356</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>362</v>
-      </c>
       <c r="C34" s="53" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A35" s="54" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C35" s="53" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A36" s="54" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C36" s="53" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C37" s="52" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="230.4" x14ac:dyDescent="0.3">
       <c r="B38" s="50" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -9193,7 +10419,7 @@
       <c r="V3" s="2"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="57" t="s">
         <v>2</v>
       </c>
     </row>
@@ -9211,7 +10437,7 @@
     </row>
     <row r="6" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13" t="s">
@@ -9223,7 +10449,7 @@
     </row>
     <row r="7" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>50</v>
@@ -9235,15 +10461,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="32" t="s">
-        <v>57</v>
+      <c r="C8" s="56" t="s">
+        <v>382</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>56</v>
@@ -9251,144 +10477,144 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>55</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B12" s="44" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A13" s="15"/>
       <c r="B13" s="44" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="33" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C14" s="43" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
     </row>
     <row r="16" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="C16" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>105</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="9"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="9"/>
     </row>
     <row r="21" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B21" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>184</v>
-      </c>
       <c r="D21" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -9397,142 +10623,142 @@
       <c r="A23" s="2"/>
       <c r="B23" s="15"/>
       <c r="C23" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="9"/>
     </row>
     <row r="25" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B26" s="12"/>
       <c r="C26" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C27" s="13"/>
     </row>
     <row r="28" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="B29" s="13"/>
       <c r="C29" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="216" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="13" t="s">
-        <v>79</v>
-      </c>
       <c r="C30" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B31" s="12"/>
       <c r="C31" s="9"/>
     </row>
     <row r="32" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B32" s="13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
       <c r="B33" s="12"/>
       <c r="C33" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
       <c r="B36" s="12"/>
       <c r="C36" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="13"/>
@@ -9540,75 +10766,75 @@
     </row>
     <row r="38" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B38" s="13" t="s">
-        <v>89</v>
-      </c>
       <c r="C38" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
       <c r="B39" s="12"/>
       <c r="C39" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D40" s="2"/>
     </row>
     <row r="41" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B41" s="12"/>
       <c r="C41" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="13" t="s">
         <v>97</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B43" s="13"/>
       <c r="C43" s="13"/>
       <c r="D43" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
       <c r="B44" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="D44" s="15" t="s">
         <v>123</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -9618,35 +10844,35 @@
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
       <c r="D45" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="216" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B46" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D46" s="41" t="s">
         <v>246</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D46" s="41" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="216" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C47" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="B47" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="C47" s="15" t="s">
-        <v>128</v>
-      </c>
       <c r="D47" s="41" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -9662,10 +10888,10 @@
         <v>20</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>19</v>
@@ -9676,10 +10902,10 @@
         <v>17</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>21</v>
@@ -9690,10 +10916,10 @@
         <v>16</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>22</v>
@@ -9704,10 +10930,10 @@
         <v>9</v>
       </c>
       <c r="B52" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="C52" s="15" t="s">
         <v>162</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>163</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>23</v>
@@ -9718,10 +10944,10 @@
         <v>18</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C53" s="15" t="s">
         <v>164</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>165</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>24</v>
@@ -9732,10 +10958,10 @@
         <v>14</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>28</v>
@@ -9743,42 +10969,42 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D55" s="15"/>
     </row>
     <row r="56" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A56" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A57" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -9786,10 +11012,10 @@
         <v>11</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>25</v>
@@ -9800,10 +11026,10 @@
         <v>12</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>27</v>
@@ -9814,10 +11040,10 @@
         <v>10</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>26</v>
@@ -9828,16 +11054,16 @@
         <v>13</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D61" s="15"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
@@ -9845,68 +11071,68 @@
     </row>
     <row r="63" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C63" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D63" s="15"/>
     </row>
     <row r="64" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C64" s="29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D64" s="15"/>
     </row>
     <row r="65" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C65" s="15" t="s">
         <v>189</v>
-      </c>
-      <c r="C65" s="15" t="s">
-        <v>190</v>
       </c>
       <c r="D65" s="15"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
       <c r="D66" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B67" s="12"/>
       <c r="C67" s="9"/>
     </row>
     <row r="68" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B68" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C68" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C68" s="15" t="s">
-        <v>184</v>
-      </c>
       <c r="D68" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
@@ -9915,15 +11141,15 @@
       <c r="A70" s="2"/>
       <c r="B70" s="15"/>
       <c r="C70" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
@@ -9933,229 +11159,229 @@
     </row>
     <row r="72" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C72" s="29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C73" s="29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D73" s="2"/>
     </row>
     <row r="74" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B74" s="29" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C74" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C75" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="C75" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C76" s="29" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C77" s="29" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C78" s="32" t="s">
         <v>209</v>
-      </c>
-      <c r="C78" s="32" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C79" s="29" t="s">
         <v>211</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C79" s="29" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="2"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C82" s="9"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C83" s="9"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C84" s="9"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C85" s="9"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C86" s="9"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C87" s="9"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A90" s="32" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B90" s="32"/>
       <c r="C90" s="32" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A91" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="B91" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="C91" s="32" t="s">
         <v>241</v>
       </c>
-      <c r="B91" s="32" t="s">
+      <c r="D91" s="32" t="s">
         <v>248</v>
-      </c>
-      <c r="C91" s="32" t="s">
-        <v>242</v>
-      </c>
-      <c r="D91" s="32" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B92" s="32" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B95" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="C95" s="32" t="s">
         <v>237</v>
-      </c>
-      <c r="B95" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="C95" s="32" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B96" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C96" s="33" t="s">
         <v>235</v>
-      </c>
-      <c r="C96" s="33" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="34" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>30</v>
@@ -10163,38 +11389,38 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C98" s="32" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="10" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C103" s="42" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="22" type="noConversion"/>
+  <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -10206,7 +11432,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:V45"/>
+  <dimension ref="A2:V49"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -10269,148 +11495,326 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B6" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="D6" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B8" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>263</v>
+        <v>262</v>
+      </c>
+      <c r="B10" s="56" t="s">
+        <v>377</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>365</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>266</v>
+      <c r="C11" s="56" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="288" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="C38" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="D38" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B40" s="2" t="s">
+    <row r="15" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B15" s="55" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="31" t="s">
+        <v>368</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C17" s="55" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B41" s="2" t="s">
+    <row r="20" spans="1:4" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="56" t="s">
+        <v>381</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B42" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B43" s="2" t="s">
+    <row r="22" spans="1:4" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="B22" s="56" t="s">
+        <v>384</v>
+      </c>
+      <c r="C22" s="56" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="58" t="s">
+        <v>385</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B24" s="56" t="s">
+        <v>387</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D24" s="56" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B25" s="60" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D25" s="56" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B26" s="60" t="s">
+        <v>401</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D26" s="60" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B27" s="60" t="s">
+        <v>404</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D27" s="60" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="58" t="s">
+        <v>409</v>
+      </c>
+      <c r="B28" s="60"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="60"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B29" s="60"/>
+      <c r="C29" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D29" s="60" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B30" s="60"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="60"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B44" s="2" t="s">
+    <row r="32" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B32" s="56" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B34" s="56" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C42" s="27"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B48" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B45" s="2" t="s">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B49" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C30:D44">
-    <sortCondition ref="D30:D44"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C34:D48">
+    <sortCondition ref="D34:D48"/>
   </sortState>
-  <phoneticPr fontId="22" type="noConversion"/>
+  <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -10452,10 +11856,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" s="55"/>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
+      <c r="A1" s="59"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="22"/>
@@ -10478,7 +11882,7 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C3" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P3" s="19"/>
       <c r="U3" s="19"/>
@@ -10486,7 +11890,7 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P4" s="19"/>
       <c r="U4" s="19"/>
@@ -10495,38 +11899,38 @@
     <row r="5" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="15"/>
@@ -10534,69 +11938,69 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:22" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:22" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C13" s="46" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:22" ht="216" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -10657,7 +12061,7 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="C3" s="11" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="P3" s="1"/>
       <c r="U3" s="1"/>
@@ -10671,7 +12075,7 @@
     <row r="5" spans="1:22" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A5" s="36"/>
       <c r="C5" s="48" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
@@ -10771,7 +12175,7 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B3" s="37"/>
       <c r="C3" s="36"/>
@@ -10781,11 +12185,11 @@
     </row>
     <row r="4" spans="1:22" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="37" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B4" s="37"/>
       <c r="C4" s="45" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
